--- a/docs/Data_Dictionary.xlsx
+++ b/docs/Data_Dictionary.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HomePC\Desktop\classification_project\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FEDFA3-164A-4A0E-BB52-34D5CF885B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,271 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="86">
+  <si>
+    <t>Column Name</t>
+  </si>
+  <si>
+    <t>Data Type</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Business Meaning</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>SK_ID_CURR</t>
+  </si>
+  <si>
+    <t>int64</t>
+  </si>
+  <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>Unique identifier assigned to each customer/application record</t>
+  </si>
+  <si>
+    <t>Not a predictive feature</t>
+  </si>
+  <si>
+    <t>TARGET</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant experienced payment difficulties/default</t>
+  </si>
+  <si>
+    <t>0 = no payment difficulties, 1 = payment difficulties</t>
+  </si>
+  <si>
+    <t>NAME_CONTRACT_TYPE</t>
+  </si>
+  <si>
+    <t>object</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>Type of loan contract associated with the application</t>
+  </si>
+  <si>
+    <t>Categorical feature</t>
+  </si>
+  <si>
+    <t>CODE_GENDER</t>
+  </si>
+  <si>
+    <t>Gender of the applicant</t>
+  </si>
+  <si>
+    <t>FLAG_OWN_CAR</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant owns a car</t>
+  </si>
+  <si>
+    <t>Binary categorical feature</t>
+  </si>
+  <si>
+    <t>FLAG_OWN_REALTY</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant owns real estate/property</t>
+  </si>
+  <si>
+    <t>CNT_CHILDREN</t>
+  </si>
+  <si>
+    <t>Number of children of the applicant</t>
+  </si>
+  <si>
+    <t>Count variable</t>
+  </si>
+  <si>
+    <t>AMT_INCOME_TOTAL</t>
+  </si>
+  <si>
+    <t>float64</t>
+  </si>
+  <si>
+    <t>Total income of the applicant</t>
+  </si>
+  <si>
+    <t>Monetary value</t>
+  </si>
+  <si>
+    <t>AMT_CREDIT</t>
+  </si>
+  <si>
+    <t>Amount of credit/loan granted to the applicant</t>
+  </si>
+  <si>
+    <t>AMT_ANNUITY</t>
+  </si>
+  <si>
+    <t>Periodic loan repayment amount associated with the application</t>
+  </si>
+  <si>
+    <t>AMT_GOODS_PRICE</t>
+  </si>
+  <si>
+    <t>Price of the goods or item being financed</t>
+  </si>
+  <si>
+    <t>NAME_TYPE_SUITE</t>
+  </si>
+  <si>
+    <t>Type of person who accompanied the applicant when applying for the loan</t>
+  </si>
+  <si>
+    <t>NAME_INCOME_TYPE</t>
+  </si>
+  <si>
+    <t>Type/source of income or employment status of the applicant</t>
+  </si>
+  <si>
+    <t>NAME_EDUCATION_TYPE</t>
+  </si>
+  <si>
+    <t>Education or qualification level of the applicant</t>
+  </si>
+  <si>
+    <t>NAME_FAMILY_STATUS</t>
+  </si>
+  <si>
+    <t>Marital/family status of the applicant</t>
+  </si>
+  <si>
+    <t>NAME_HOUSING_TYPE</t>
+  </si>
+  <si>
+    <t>Type of housing/accommodation in which the applicant lives</t>
+  </si>
+  <si>
+    <t>REGION_POPULATION_RELATIVE</t>
+  </si>
+  <si>
+    <t>Normalized measure of the population density of the applicant's region</t>
+  </si>
+  <si>
+    <t>Relative regional population measure</t>
+  </si>
+  <si>
+    <t>DAYS_BIRTH</t>
+  </si>
+  <si>
+    <t>Number of days between the applicant's birth date and the loan application date</t>
+  </si>
+  <si>
+    <t>Negative values are expected; can be transformed into age</t>
+  </si>
+  <si>
+    <t>DAYS_EMPLOYED</t>
+  </si>
+  <si>
+    <t>Duration of the applicant's employment before the loan application, measured in days</t>
+  </si>
+  <si>
+    <t>Negative values are expected; 365243 is a special/unknown value</t>
+  </si>
+  <si>
+    <t>DAYS_REGISTRATION</t>
+  </si>
+  <si>
+    <t>Number of days between the applicant's registration date and the loan application date</t>
+  </si>
+  <si>
+    <t>Negative values indicate registration occurred before the application</t>
+  </si>
+  <si>
+    <t>DAYS_ID_PUBLISH</t>
+  </si>
+  <si>
+    <t>Number of days between the applicant's ID document publication/issuance date and the loan application date</t>
+  </si>
+  <si>
+    <t>Negative values indicate the ID was published before the application</t>
+  </si>
+  <si>
+    <t>OWN_CAR_AGE</t>
+  </si>
+  <si>
+    <t>Age of the car owned by the applicant, measured in years</t>
+  </si>
+  <si>
+    <t>Represents vehicle age, not duration of ownership</t>
+  </si>
+  <si>
+    <t>FLAG_MOBIL</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant has/provides a mobile phone number</t>
+  </si>
+  <si>
+    <t>Binary indicator</t>
+  </si>
+  <si>
+    <t>FLAG_EMP_PHONE</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant has/provides a work/employment phone number</t>
+  </si>
+  <si>
+    <t>FLAG_WORK_PHONE</t>
+  </si>
+  <si>
+    <t>Indicates whether a work phone number is available/provided</t>
+  </si>
+  <si>
+    <t>FLAG_CONT_MOBILE</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant is reachable through their mobile phone</t>
+  </si>
+  <si>
+    <t>OCCUPATION_TYPE</t>
+  </si>
+  <si>
+    <t>Occupation type of the applicant</t>
+  </si>
+  <si>
+    <t>Categorical feature; contains missing values</t>
+  </si>
+  <si>
+    <t>CNT_FAM_MEMBERS</t>
+  </si>
+  <si>
+    <t>Number of family members associated with the applicant</t>
+  </si>
+  <si>
+    <t>FLAG_PHONE</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant has provided a phone number</t>
+  </si>
+  <si>
+    <t>Binary indicator; 1 = yes, 0 = no</t>
+  </si>
+  <si>
+    <t>FLAG_EMAIL</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant has provided an email address</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,10 +599,543 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="27.90625" customWidth="1"/>
+    <col min="4" max="4" width="74.6328125" customWidth="1"/>
+    <col min="5" max="5" width="43.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" t="s">
+        <v>65</v>
+      </c>
+      <c r="E23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>67</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" t="s">
+        <v>68</v>
+      </c>
+      <c r="E24" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" t="s">
+        <v>71</v>
+      </c>
+      <c r="E25" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" t="s">
+        <v>77</v>
+      </c>
+      <c r="E30" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>79</v>
+      </c>
+      <c r="B31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" t="s">
+        <v>80</v>
+      </c>
+      <c r="E31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/Data_Dictionary.xlsx
+++ b/docs/Data_Dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HomePC\Desktop\classification_project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FEDFA3-164A-4A0E-BB52-34D5CF885B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BABDD48-9026-4ED9-9A43-AB50E8870DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="296">
   <si>
     <t>Column Name</t>
   </si>
@@ -283,19 +283,654 @@
   </si>
   <si>
     <t>Indicates whether the applicant has provided an email address</t>
+  </si>
+  <si>
+    <t>REGION_RATING_CLIENT</t>
+  </si>
+  <si>
+    <t>Rating of the region where the applicant lives</t>
+  </si>
+  <si>
+    <t>Ordinal feature; represents the regional rating associated with the applicant</t>
+  </si>
+  <si>
+    <t>REGION_RATING_CLIENT_W_CITY</t>
+  </si>
+  <si>
+    <t>Rating of the applicant's region considering the city where the applicant lives</t>
+  </si>
+  <si>
+    <t>Ordinal feature; represents the regional rating associated with the applicant's city</t>
+  </si>
+  <si>
+    <t>WEEKDAY_APPR_PROCESS_START</t>
+  </si>
+  <si>
+    <t>Day of the week on which the applicant's application process was started</t>
+  </si>
+  <si>
+    <t>Categorical feature; values represent days of the week</t>
+  </si>
+  <si>
+    <t>HOUR_APPR_PROCESS_START</t>
+  </si>
+  <si>
+    <t>Hour of the day when the applicant's application process was started</t>
+  </si>
+  <si>
+    <t>Numerical feature; represents the hour of application initiation</t>
+  </si>
+  <si>
+    <t>REG_REGION_NOT_LIVE_REGION</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant's registered region is different from their living region</t>
+  </si>
+  <si>
+    <t>Binary feature; 1 = different region, 0 = same region</t>
+  </si>
+  <si>
+    <t>REG_REGION_NOT_WORK_REGION</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant's registered region is different from their work region</t>
+  </si>
+  <si>
+    <t>LIVE_REGION_NOT_WORK_REGION</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant's living region is different from their work region</t>
+  </si>
+  <si>
+    <t>REG_CITY_NOT_LIVE_CITY</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant's registered city is different from their living city</t>
+  </si>
+  <si>
+    <t>Binary feature; 1 = different city, 0 = same city</t>
+  </si>
+  <si>
+    <t>LIVE_CITY_NOT_WORK_CITY</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant's living city is different from their work city</t>
+  </si>
+  <si>
+    <t>ORGANIZATION_TYPE</t>
+  </si>
+  <si>
+    <t>Type of organization or industry where the applicant works</t>
+  </si>
+  <si>
+    <t>Categorical feature; contains different organization/industry categories</t>
+  </si>
+  <si>
+    <t>EXT_SOURCE_1</t>
+  </si>
+  <si>
+    <t>Normalized score from an external data source related to the applicant</t>
+  </si>
+  <si>
+    <t>Continuous numerical feature; higher values generally indicate a stronger applicant</t>
+  </si>
+  <si>
+    <t>EXT_SOURCE_2</t>
+  </si>
+  <si>
+    <t>Normalized score from a second external data source related to the applicant</t>
+  </si>
+  <si>
+    <t>EXT_SOURCE_3</t>
+  </si>
+  <si>
+    <t>Normalized score from a third external data source related to the applicant</t>
+  </si>
+  <si>
+    <t>APARTMENTS_AVG</t>
+  </si>
+  <si>
+    <t>Normalized average size of apartments in the applicant's building</t>
+  </si>
+  <si>
+    <t>Continuous feature; normalized value</t>
+  </si>
+  <si>
+    <t>BASEMENTAREA_AVG</t>
+  </si>
+  <si>
+    <t>Normalized average basement area of the applicant's building</t>
+  </si>
+  <si>
+    <t>YEARS_BEGINEXPLUATATION_AVG</t>
+  </si>
+  <si>
+    <t>Normalized average number of years since the building began being used</t>
+  </si>
+  <si>
+    <t>YEARS_BUILD_AVG</t>
+  </si>
+  <si>
+    <t>Normalized average number of years since the building was built</t>
+  </si>
+  <si>
+    <t>COMMONAREA_AVG</t>
+  </si>
+  <si>
+    <t>Normalized average size of the common area in the applicant's building</t>
+  </si>
+  <si>
+    <t>ELEVATORS_AVG</t>
+  </si>
+  <si>
+    <t>Normalized average number of elevators in the applicant's building</t>
+  </si>
+  <si>
+    <t>ENTRANCES_AVG</t>
+  </si>
+  <si>
+    <t>Normalized average number of entrances in the applicant's building</t>
+  </si>
+  <si>
+    <t>FLOORS_MAX_AVG</t>
+  </si>
+  <si>
+    <t>Indicates the average maximum number of floors of the buildings associated with the property</t>
+  </si>
+  <si>
+    <t>Derived from building/property information; continuous numerical feature</t>
+  </si>
+  <si>
+    <t>FLOORSMIN_AVG</t>
+  </si>
+  <si>
+    <t>Indicates the average minimum number of floors of the buildings associated with the property</t>
+  </si>
+  <si>
+    <t>Aggregated building/property characteristic; continuous numerical feature</t>
+  </si>
+  <si>
+    <t>LANDAREA_AVG</t>
+  </si>
+  <si>
+    <t>Indicates the average land area of the building/property</t>
+  </si>
+  <si>
+    <t>Aggregated property characteristic; continuous numerical feature</t>
+  </si>
+  <si>
+    <t>LIVINGAPARTMENTS_AVG</t>
+  </si>
+  <si>
+    <t>Indicates the average number of apartments intended for residential living in the building</t>
+  </si>
+  <si>
+    <t>Aggregated building characteristic; continuous numerical feature</t>
+  </si>
+  <si>
+    <t>LIVINGAREA_AVG</t>
+  </si>
+  <si>
+    <t>Indicates the average living area of the property/building</t>
+  </si>
+  <si>
+    <t>NONLIVINGAPARTMENTS_AVG</t>
+  </si>
+  <si>
+    <t>Indicates the average number of non-residential apartments in the building</t>
+  </si>
+  <si>
+    <t>NONLIVINGAREA_AVG</t>
+  </si>
+  <si>
+    <t>Indicates the average non-living area of the building/property</t>
+  </si>
+  <si>
+    <t>APARTMENTS_MODE</t>
+  </si>
+  <si>
+    <t>Indicates the most frequently occurring value for the number/proportion of apartments in the building/property</t>
+  </si>
+  <si>
+    <t>Aggregated building/property characteristic; mode value</t>
+  </si>
+  <si>
+    <t>BASEMENTAREA_MODE</t>
+  </si>
+  <si>
+    <t>Indicates the most frequently occurring basement area of the building/property</t>
+  </si>
+  <si>
+    <t>YEARS_BEGINEXPLUATATION_MODE</t>
+  </si>
+  <si>
+    <t>Indicates the most frequently occurring year in which the building/property began exploitation or use</t>
+  </si>
+  <si>
+    <t>YEARS_BUILD_MODE</t>
+  </si>
+  <si>
+    <t>Indicates the most frequently occurring year in which the building/property was built</t>
+  </si>
+  <si>
+    <t>COMMONAREA_MODE</t>
+  </si>
+  <si>
+    <t>Indicates the most frequently occurring common area of the building/property</t>
+  </si>
+  <si>
+    <t>ELEVATORS_MODE</t>
+  </si>
+  <si>
+    <t>Indicates the most frequently occurring number of elevators in the building/property</t>
+  </si>
+  <si>
+    <t>ENTRANCES_MODE</t>
+  </si>
+  <si>
+    <t>Indicates the most frequently occurring number of entrances in the building/property</t>
+  </si>
+  <si>
+    <t>FLOORSMAX_MODE</t>
+  </si>
+  <si>
+    <t>Indicates the most frequently occurring maximum number of floors in the building/property</t>
+  </si>
+  <si>
+    <t>FLOORSMIN_MODE</t>
+  </si>
+  <si>
+    <t>Indicates the most frequently occurring minimum number of floors in the building/property</t>
+  </si>
+  <si>
+    <t>LANDAREA_MODE</t>
+  </si>
+  <si>
+    <t>Indicates the most frequently occurring land area of the building/property</t>
+  </si>
+  <si>
+    <t>LIVINGAPARTMENTS_MODE</t>
+  </si>
+  <si>
+    <t>Indicates the most frequently occurring number/proportion of apartments intended for residential living in the building</t>
+  </si>
+  <si>
+    <t>Aggregated building characteristic; mode value</t>
+  </si>
+  <si>
+    <t>LIVINGAREA_MODE</t>
+  </si>
+  <si>
+    <t>Indicates the most frequently occurring living area of the building/property</t>
+  </si>
+  <si>
+    <t>Aggregated property characteristic; mode value</t>
+  </si>
+  <si>
+    <t>NONLIVINGAPARTMENTS_MODE</t>
+  </si>
+  <si>
+    <t>Indicates the most frequently occurring number of non-residential apartments in the building</t>
+  </si>
+  <si>
+    <t>NONLIVINGAREA_MODE</t>
+  </si>
+  <si>
+    <t>Indicates the most frequently occurring non-living area of the building/property</t>
+  </si>
+  <si>
+    <t>APARTMENTS_MEDI</t>
+  </si>
+  <si>
+    <t>Indicates the median number/proportion of apartments in the building/property</t>
+  </si>
+  <si>
+    <t>Aggregated building/property characteristic; median value</t>
+  </si>
+  <si>
+    <t>BASEMENTAREA_MEDI</t>
+  </si>
+  <si>
+    <t>Indicates the median basement area of the building/property</t>
+  </si>
+  <si>
+    <t>YEARS_BEGINEXPLUATATION_MEDI</t>
+  </si>
+  <si>
+    <t>Indicates the median year in which the building/property began exploitation or use</t>
+  </si>
+  <si>
+    <t>YEARS_BUILD_MEDI</t>
+  </si>
+  <si>
+    <t>Indicates the median year in which the building/property was built</t>
+  </si>
+  <si>
+    <t>COMMONAREA_MEDI</t>
+  </si>
+  <si>
+    <t>Indicates the median common area of the building/property</t>
+  </si>
+  <si>
+    <t>ELEVATORS_MEDI</t>
+  </si>
+  <si>
+    <t>Indicates the median number of elevators in the building/property</t>
+  </si>
+  <si>
+    <t>ENTRANCES_MEDI</t>
+  </si>
+  <si>
+    <t>Indicates the median number of entrances in the building/property</t>
+  </si>
+  <si>
+    <t>FLOORSMAX_MEDI</t>
+  </si>
+  <si>
+    <t>Indicates the median maximum number of floors in the building/property</t>
+  </si>
+  <si>
+    <t>FLOORSMIN_MEDI</t>
+  </si>
+  <si>
+    <t>Indicates the median minimum number of floors in the building/property</t>
+  </si>
+  <si>
+    <t>LANDAREA_MEDI</t>
+  </si>
+  <si>
+    <t>Indicates the median land area of the building/property</t>
+  </si>
+  <si>
+    <t>Aggregated property characteristic; median value</t>
+  </si>
+  <si>
+    <t>LIVINGAPARTMENTS_MEDI</t>
+  </si>
+  <si>
+    <t>Indicates the median number/proportion of apartments intended for residential living in the building</t>
+  </si>
+  <si>
+    <t>Aggregated building characteristic; median value</t>
+  </si>
+  <si>
+    <t>LIVINGAREA_MEDI</t>
+  </si>
+  <si>
+    <t>Indicates the median living area of the building/property</t>
+  </si>
+  <si>
+    <t>NONLIVINGAPARTMENTS_MEDI</t>
+  </si>
+  <si>
+    <t>Indicates the median number of non-residential apartments in the building</t>
+  </si>
+  <si>
+    <t>NONLIVINGAREA_MEDI</t>
+  </si>
+  <si>
+    <t>Indicates the median non-living area of the building/property</t>
+  </si>
+  <si>
+    <t>FONDKAPREMONT_MODE</t>
+  </si>
+  <si>
+    <t>Indicates the mode of the building's fund for capital repairs or maintenance</t>
+  </si>
+  <si>
+    <t>Categorical building/property characteristic; most frequently occurring category</t>
+  </si>
+  <si>
+    <t>HOUSETYPE_MODE</t>
+  </si>
+  <si>
+    <t>Indicates the most frequently occurring type of house/building</t>
+  </si>
+  <si>
+    <t>Categorical building/property characteristic; mode value</t>
+  </si>
+  <si>
+    <t>TOTALAREA_MODE</t>
+  </si>
+  <si>
+    <t>Indicates the most frequently occurring total area of the building/property</t>
+  </si>
+  <si>
+    <t>WALLSMATERIAL_MODE</t>
+  </si>
+  <si>
+    <t>Indicates the most frequently occurring type of wall material used in the building</t>
+  </si>
+  <si>
+    <t>EMERGENCYSTATE_MODE</t>
+  </si>
+  <si>
+    <t>Indicates whether the building/property is in an emergency state</t>
+  </si>
+  <si>
+    <t>Categorical property characteristic; mode value</t>
+  </si>
+  <si>
+    <t>OBS_30_CNT_SOCIAL_CIRCLE</t>
+  </si>
+  <si>
+    <t>Indicates the number of people in the applicant's social circle who were observed to have payment difficulties of 30 or more days</t>
+  </si>
+  <si>
+    <t>Social-circle credit behavior feature; numerical count</t>
+  </si>
+  <si>
+    <t>DEF_30_CNT_SOCIAL_CIRCLE</t>
+  </si>
+  <si>
+    <t>Indicates the number of people in the applicant's social circle who were 30 or more days past due</t>
+  </si>
+  <si>
+    <t>Social-circle credit risk feature; numerical count</t>
+  </si>
+  <si>
+    <t>OBS_60_CNT_SOCIAL_CIRCLE</t>
+  </si>
+  <si>
+    <t>Indicates the number of people in the applicant's social circle who were observed to have payment difficulties of 60 or more days</t>
+  </si>
+  <si>
+    <t>DEF_60_CNT_SOCIAL_CIRCLE</t>
+  </si>
+  <si>
+    <t>Indicates the number of people in the applicant's social circle who have defaulted or had payment difficulties of more than 60 days</t>
+  </si>
+  <si>
+    <t>DAYS_LAST_PHONE_CHANGE</t>
+  </si>
+  <si>
+    <t>Indicates the number of days before the application since the applicant last changed their phone number</t>
+  </si>
+  <si>
+    <t>Time-related feature; negative values generally represent days before the application</t>
+  </si>
+  <si>
+    <t>FLAG_DOCUMENT_2</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant provided the document corresponding to document type 2</t>
+  </si>
+  <si>
+    <t>Binary indicator; 1 = provided, 0 = not provided</t>
+  </si>
+  <si>
+    <t>FLAG_DOCUMENT_3</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant provided the document corresponding to document type 3</t>
+  </si>
+  <si>
+    <t>FLAG_DOCUMENT_4</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant provided the document corresponding to document type 4</t>
+  </si>
+  <si>
+    <t>FLAG_DOCUMENT_5</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant provided the document corresponding to document type 5</t>
+  </si>
+  <si>
+    <t>FLAG_DOCUMENT_6</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant provided the document corresponding to document type 6</t>
+  </si>
+  <si>
+    <t>FLAG_DOCUMENT_7</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant provided the document corresponding to document type 7</t>
+  </si>
+  <si>
+    <t>FLAG_DOCUMENT_8</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant provided the document corresponding to document type 8</t>
+  </si>
+  <si>
+    <t>FLAG_DOCUMENT_9</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant provided the document corresponding to document type 9</t>
+  </si>
+  <si>
+    <t>FLAG_DOCUMENT_10</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant provided the document corresponding to document type 10</t>
+  </si>
+  <si>
+    <t>FLAG_DOCUMENT_11</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant provided the document corresponding to document type 11</t>
+  </si>
+  <si>
+    <t>FLAG_DOCUMENT_12</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant provided the document corresponding to document type 12</t>
+  </si>
+  <si>
+    <t>FLAG_DOCUMENT_13</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant provided the document corresponding to document type 13</t>
+  </si>
+  <si>
+    <t>FLAG_DOCUMENT_14</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant provided the document corresponding to document type 14</t>
+  </si>
+  <si>
+    <t>FLAG_DOCUMENT_15</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant provided the document corresponding to document type 15</t>
+  </si>
+  <si>
+    <t>FLAG_DOCUMENT_16</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant provided the document corresponding to document type 16</t>
+  </si>
+  <si>
+    <t>FLAG_DOCUMENT_17</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant provided the document corresponding to document type 17</t>
+  </si>
+  <si>
+    <t>FLAG_DOCUMENT_18</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant provided the document corresponding to document type 18</t>
+  </si>
+  <si>
+    <t>FLAG_DOCUMENT_19</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant provided the document corresponding to document type 19</t>
+  </si>
+  <si>
+    <t>FLAG_DOCUMENT_20</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant provided the document corresponding to document type 20</t>
+  </si>
+  <si>
+    <t>FLAG_DOCUMENT_21</t>
+  </si>
+  <si>
+    <t>Indicates whether the applicant provided the document corresponding to document type 21</t>
+  </si>
+  <si>
+    <t>Binary indicator; 1 = provided,</t>
+  </si>
+  <si>
+    <t>AMT_REQ_CREDIT_BUREAU_HOUR</t>
+  </si>
+  <si>
+    <t>Indicates the number of credit bureau enquiries made about the applicant within the previous hour</t>
+  </si>
+  <si>
+    <t>Credit bureau enquiry feature; numerical count</t>
+  </si>
+  <si>
+    <t>AMT_REQ_CREDIT_BUREAU_DAY</t>
+  </si>
+  <si>
+    <t>Indicates the number of credit bureau enquiries made about the applicant within the previous day</t>
+  </si>
+  <si>
+    <t>AMT_REQ_CREDIT_BUREAU_WEEK</t>
+  </si>
+  <si>
+    <t>Indicates the number of credit bureau enquiries made about the applicant within the previous week</t>
+  </si>
+  <si>
+    <t>AMT_REQ_CREDIT_BUREAU_MON</t>
+  </si>
+  <si>
+    <t>Indicates the number of credit bureau enquiries made about the applicant within the previous month</t>
+  </si>
+  <si>
+    <t>AMT_REQ_CREDIT_BUREAU_QRT</t>
+  </si>
+  <si>
+    <t>Indicates the number of credit bureau enquiries made about the applicant within the previous quarter</t>
+  </si>
+  <si>
+    <t>AMT_REQ_CREDIT_BUREAU_YEAR</t>
+  </si>
+  <si>
+    <t>Indicates the number of credit bureau enquiries made about the applicant within the previous year</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -318,8 +953,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -600,539 +1245,2106 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E123"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="27.90625" customWidth="1"/>
-    <col min="4" max="4" width="74.6328125" customWidth="1"/>
-    <col min="5" max="5" width="43.81640625" customWidth="1"/>
+    <col min="1" max="1" width="25.7265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="93.90625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.26953125" style="4" customWidth="1"/>
+    <col min="6" max="16384" width="8.7265625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="4" spans="1:5">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="6" spans="1:5">
+      <c r="A6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="7" spans="1:5">
+      <c r="A7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="8" spans="1:5">
+      <c r="A8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="B8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="9" spans="1:5">
+      <c r="A9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="B9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="10" spans="1:5">
+      <c r="A10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="B10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="11" spans="1:5">
+      <c r="A11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="B11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="12" spans="1:5">
+      <c r="A12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="B12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="13" spans="1:5">
+      <c r="A13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="C13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    <row r="14" spans="1:5">
+      <c r="A14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="C14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+    <row r="15" spans="1:5">
+      <c r="A15" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="C15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+    <row r="16" spans="1:5">
+      <c r="A16" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="C16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+    <row r="17" spans="1:5">
+      <c r="A17" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C17" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="C17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+    <row r="18" spans="1:5">
+      <c r="A18" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="B18" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+    <row r="19" spans="1:5">
+      <c r="A19" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="B19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+    <row r="20" spans="1:5">
+      <c r="A20" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B20" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="B20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+    <row r="21" spans="1:5">
+      <c r="A21" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B21" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="B21" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+    <row r="22" spans="1:5">
+      <c r="A22" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="B22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+    <row r="23" spans="1:5">
+      <c r="A23" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B23" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="B23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+    <row r="24" spans="1:5">
+      <c r="A24" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B24" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="B24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+    <row r="25" spans="1:5">
+      <c r="A25" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B25" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" t="s">
-        <v>16</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="B25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+    <row r="26" spans="1:5">
+      <c r="A26" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="B26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+    <row r="27" spans="1:5">
+      <c r="A27" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B27" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="B27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+    <row r="28" spans="1:5">
+      <c r="A28" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B28" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" t="s">
-        <v>16</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="B28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="4" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+    <row r="29" spans="1:5">
+      <c r="A29" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B29" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" t="s">
-        <v>16</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="B29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="4" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+    <row r="30" spans="1:5">
+      <c r="A30" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C30" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="C30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+    <row r="31" spans="1:5">
+      <c r="A31" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B31" t="s">
-        <v>30</v>
-      </c>
-      <c r="C31" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="B31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="4" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="29">
+      <c r="A33" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="29">
+      <c r="A34" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="29">
+      <c r="A35" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="29">
+      <c r="A36" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="29">
+      <c r="A37" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="29">
+      <c r="A38" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="29">
+      <c r="A57" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="29">
+      <c r="A59" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="29">
+      <c r="A61" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="29">
+      <c r="A69" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="29">
+      <c r="A71" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="29">
+      <c r="A75" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="29">
+      <c r="A85" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="29">
+      <c r="A92" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="29">
+      <c r="A94" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="29">
+      <c r="A95" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="29">
+      <c r="A96" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="25">
+      <c r="A117" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="25">
+      <c r="A118" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="25">
+      <c r="A119" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="25">
+      <c r="A120" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="25">
+      <c r="A121" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="25">
+      <c r="A122" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="25">
+      <c r="A123" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>285</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Data_Dictionary.xlsx
+++ b/docs/Data_Dictionary.xlsx
@@ -953,7 +953,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -961,10 +961,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1248,1643 +1244,1642 @@
   <dimension ref="A1:E123"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="25.7265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1796875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.453125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="93.90625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.26953125" style="4" customWidth="1"/>
-    <col min="6" max="16384" width="8.7265625" style="4"/>
+    <col min="1" max="1" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="93.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="4" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="4" t="s">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
+      <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="4" t="s">
+      <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="4" t="s">
+      <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="4" t="s">
+      <c r="A6" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="4" t="s">
+      <c r="A7" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="4" t="s">
+      <c r="A8" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="4" t="s">
+      <c r="A9" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="4" t="s">
+      <c r="A10" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="4" t="s">
+      <c r="A11" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="4" t="s">
+      <c r="A12" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="4" t="s">
+      <c r="A13" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="4" t="s">
+      <c r="A14" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="C14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="4" t="s">
+      <c r="A15" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="C15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="4" t="s">
+      <c r="A16" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="4" t="s">
+      <c r="A17" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="4" t="s">
+      <c r="A18" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="4" t="s">
+      <c r="A19" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="4" t="s">
+      <c r="A20" t="s">
         <v>55</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="4" t="s">
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="4" t="s">
+      <c r="A21" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" s="4" t="s">
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" t="s">
         <v>59</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="4" t="s">
+      <c r="A22" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="4" t="s">
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" t="s">
         <v>62</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="4" t="s">
+      <c r="A23" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="4" t="s">
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" t="s">
         <v>65</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="4" t="s">
+      <c r="A24" t="s">
         <v>67</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" t="s">
         <v>68</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="4" t="s">
+      <c r="A25" t="s">
         <v>70</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D25" s="4" t="s">
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" t="s">
         <v>71</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="4" t="s">
+      <c r="A26" t="s">
         <v>72</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" s="4" t="s">
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" t="s">
         <v>73</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="4" t="s">
+      <c r="A27" t="s">
         <v>74</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D27" s="4" t="s">
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" t="s">
         <v>75</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="4" t="s">
+      <c r="A28" t="s">
         <v>81</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D28" s="4" t="s">
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" t="s">
         <v>82</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="4" t="s">
+      <c r="A29" t="s">
         <v>84</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D29" s="4" t="s">
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" t="s">
         <v>85</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="4" t="s">
+      <c r="A30" t="s">
         <v>76</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" s="4" t="s">
+      <c r="C30" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="4" t="s">
+      <c r="A31" t="s">
         <v>79</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" s="4" t="s">
+      <c r="B31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" t="s">
         <v>80</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D32" s="3" t="s">
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="29">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D33" s="3" t="s">
+      <c r="B33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="29">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D34" s="3" t="s">
+      <c r="C34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="29">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D35" s="3" t="s">
+      <c r="B35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="29">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D36" s="3" t="s">
+      <c r="B36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="1" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="29">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D37" s="3" t="s">
+      <c r="B37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="1" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="29">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D38" s="3" t="s">
+      <c r="B38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="1" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D39" s="3" t="s">
+      <c r="B39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" s="1" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D40" s="3" t="s">
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" s="1" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="4" t="s">
+      <c r="A41" t="s">
         <v>110</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" t="s">
         <v>15</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D41" s="4" t="s">
+      <c r="C41" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" t="s">
         <v>111</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="4" t="s">
+      <c r="A42" t="s">
         <v>113</v>
       </c>
-      <c r="B42" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D42" s="4" t="s">
+      <c r="B42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" t="s">
+        <v>16</v>
+      </c>
+      <c r="D42" t="s">
         <v>114</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="4" t="s">
+      <c r="A43" t="s">
         <v>116</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D43" s="4" t="s">
+      <c r="B43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" t="s">
+        <v>16</v>
+      </c>
+      <c r="D43" t="s">
         <v>117</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="4" t="s">
+      <c r="A44" t="s">
         <v>118</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D44" s="4" t="s">
+      <c r="B44" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" t="s">
         <v>119</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="4" t="s">
+      <c r="A45" t="s">
         <v>120</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D45" s="4" t="s">
+      <c r="B45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C45" t="s">
+        <v>16</v>
+      </c>
+      <c r="D45" t="s">
         <v>121</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="4" t="s">
+      <c r="A46" t="s">
         <v>123</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D46" s="4" t="s">
+      <c r="B46" t="s">
+        <v>30</v>
+      </c>
+      <c r="C46" t="s">
+        <v>16</v>
+      </c>
+      <c r="D46" t="s">
         <v>124</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="4" t="s">
+      <c r="A47" t="s">
         <v>125</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D47" s="4" t="s">
+      <c r="B47" t="s">
+        <v>30</v>
+      </c>
+      <c r="C47" t="s">
+        <v>16</v>
+      </c>
+      <c r="D47" t="s">
         <v>126</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="4" t="s">
+      <c r="A48" t="s">
         <v>127</v>
       </c>
-      <c r="B48" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D48" s="4" t="s">
+      <c r="B48" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48" t="s">
         <v>128</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="4" t="s">
+      <c r="A49" t="s">
         <v>129</v>
       </c>
-      <c r="B49" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D49" s="4" t="s">
+      <c r="B49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" t="s">
         <v>130</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="E49" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="4" t="s">
+      <c r="A50" t="s">
         <v>131</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D50" s="4" t="s">
+      <c r="B50" t="s">
+        <v>30</v>
+      </c>
+      <c r="C50" t="s">
+        <v>16</v>
+      </c>
+      <c r="D50" t="s">
         <v>132</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E50" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="4" t="s">
+      <c r="A51" t="s">
         <v>133</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D51" s="4" t="s">
+      <c r="B51" t="s">
+        <v>30</v>
+      </c>
+      <c r="C51" t="s">
+        <v>16</v>
+      </c>
+      <c r="D51" t="s">
         <v>134</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D52" s="3" t="s">
+      <c r="B52" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="E52" s="1" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D53" s="3" t="s">
+      <c r="B53" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="E53" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
+      <c r="A54" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D54" s="3" t="s">
+      <c r="B54" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="E54" s="1" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D55" s="3" t="s">
+      <c r="B55" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="E55" s="1" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
+      <c r="A56" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D56" s="3" t="s">
+      <c r="B56" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="E56" s="1" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="29">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D57" s="3" t="s">
+      <c r="B57" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="E57" s="1" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
+      <c r="A58" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D58" s="3" t="s">
+      <c r="B58" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="E58" s="1" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="29">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D59" s="3" t="s">
+      <c r="B59" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="E59" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D60" s="3" t="s">
+      <c r="B60" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="E60" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="29">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D61" s="3" t="s">
+      <c r="B61" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E61" s="3" t="s">
+      <c r="E61" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
+      <c r="A62" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D62" s="3" t="s">
+      <c r="B62" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="E62" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D63" s="3" t="s">
+      <c r="B63" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="E63" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
+      <c r="A64" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D64" s="3" t="s">
+      <c r="B64" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E64" s="3" t="s">
+      <c r="E64" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D65" s="3" t="s">
+      <c r="B65" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="E65" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
+      <c r="A66" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D66" s="3" t="s">
+      <c r="B66" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="E66" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D67" s="3" t="s">
+      <c r="B67" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="E67" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
+      <c r="A68" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D68" s="3" t="s">
+      <c r="B68" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="E68" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="29">
-      <c r="A69" s="3" t="s">
+      <c r="A69" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D69" s="3" t="s">
+      <c r="B69" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="E69" s="1" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
+      <c r="A70" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D70" s="3" t="s">
+      <c r="B70" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="E70" s="1" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="29">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D71" s="3" t="s">
+      <c r="B71" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="E71" s="1" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
+      <c r="A72" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D72" s="3" t="s">
+      <c r="B72" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="E72" s="1" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="3" t="s">
+      <c r="A73" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D73" s="3" t="s">
+      <c r="B73" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E73" s="3" t="s">
+      <c r="E73" s="1" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="3" t="s">
+      <c r="A74" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D74" s="3" t="s">
+      <c r="B74" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E74" s="3" t="s">
+      <c r="E74" s="1" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="29">
-      <c r="A75" s="3" t="s">
+      <c r="A75" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D75" s="3" t="s">
+      <c r="B75" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E75" s="3" t="s">
+      <c r="E75" s="1" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="3" t="s">
+      <c r="A76" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B76" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D76" s="3" t="s">
+      <c r="B76" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E76" s="3" t="s">
+      <c r="E76" s="1" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="3" t="s">
+      <c r="A77" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D77" s="3" t="s">
+      <c r="B77" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E77" s="3" t="s">
+      <c r="E77" s="1" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="3" t="s">
+      <c r="A78" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D78" s="3" t="s">
+      <c r="B78" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E78" s="3" t="s">
+      <c r="E78" s="1" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="3" t="s">
+      <c r="A79" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D79" s="3" t="s">
+      <c r="B79" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E79" s="3" t="s">
+      <c r="E79" s="1" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="80" spans="1:5">
-      <c r="A80" s="3" t="s">
+      <c r="A80" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D80" s="3" t="s">
+      <c r="B80" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E80" s="3" t="s">
+      <c r="E80" s="1" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="3" t="s">
+      <c r="A81" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D81" s="3" t="s">
+      <c r="B81" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="E81" s="1" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="3" t="s">
+      <c r="A82" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D82" s="3" t="s">
+      <c r="B82" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E82" s="3" t="s">
+      <c r="E82" s="1" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B83" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D83" s="3" t="s">
+      <c r="B83" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="E83" s="1" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="3" t="s">
+      <c r="A84" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B84" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D84" s="3" t="s">
+      <c r="B84" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E84" s="3" t="s">
+      <c r="E84" s="1" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="29">
-      <c r="A85" s="3" t="s">
+      <c r="A85" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D85" s="3" t="s">
+      <c r="B85" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E85" s="3" t="s">
+      <c r="E85" s="1" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="3" t="s">
+      <c r="A86" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D86" s="3" t="s">
+      <c r="B86" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E86" s="3" t="s">
+      <c r="E86" s="1" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="87" spans="1:5">
-      <c r="A87" s="3" t="s">
+      <c r="A87" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C87" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D87" s="3" t="s">
+      <c r="C87" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="E87" s="3" t="s">
+      <c r="E87" s="1" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="88" spans="1:5">
-      <c r="A88" s="3" t="s">
+      <c r="A88" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B88" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C88" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D88" s="3" t="s">
+      <c r="C88" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="E88" s="3" t="s">
+      <c r="E88" s="1" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="3" t="s">
+      <c r="A89" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B89" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D89" s="3" t="s">
+      <c r="B89" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="E89" s="3" t="s">
+      <c r="E89" s="1" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="3" t="s">
+      <c r="A90" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B90" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C90" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D90" s="3" t="s">
+      <c r="C90" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="E90" s="3" t="s">
+      <c r="E90" s="1" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="3" t="s">
+      <c r="A91" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B91" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D91" s="3" t="s">
+      <c r="C91" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="E91" s="3" t="s">
+      <c r="E91" s="1" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="29">
-      <c r="A92" s="3" t="s">
+      <c r="A92" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B92" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D92" s="3" t="s">
+      <c r="B92" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="E92" s="3" t="s">
+      <c r="E92" s="1" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="93" spans="1:5">
-      <c r="A93" s="3" t="s">
+      <c r="A93" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D93" s="3" t="s">
+      <c r="B93" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="E93" s="3" t="s">
+      <c r="E93" s="1" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="29">
-      <c r="A94" s="3" t="s">
+      <c r="A94" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B94" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D94" s="3" t="s">
+      <c r="B94" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="E94" s="3" t="s">
+      <c r="E94" s="1" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="29">
-      <c r="A95" s="3" t="s">
+      <c r="A95" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D95" s="3" t="s">
+      <c r="B95" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="E95" s="3" t="s">
+      <c r="E95" s="1" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="29">
-      <c r="A96" s="3" t="s">
+      <c r="A96" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B96" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D96" s="3" t="s">
+      <c r="B96" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E96" s="3" t="s">
+      <c r="E96" s="1" t="s">
         <v>240</v>
       </c>
     </row>
